--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00935-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00935-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3063567B-E1A0-43C7-AA1D-CEC356FC0C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F93E3124-ED1D-4EEF-8B2E-50B4C25ED8A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{1D40B3CF-7AB8-48AF-85E4-F998B379FCB8}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{0B6A3AF5-F6CE-48DC-BBAE-67464C8F04C7}"/>
   </bookViews>
   <sheets>
     <sheet name="00935-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1442,20 +1442,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD583BCB-ED7E-4BAB-B078-914D462587BC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFB39F67-B952-4C24-A971-C75B454EC605}">
   <dimension ref="A1:R10"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.21875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1483,7 +1483,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1513,7 +1513,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1559,7 +1559,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1609,7 +1609,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1663,7 +1663,7 @@
         <v>5.63</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>2.83</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2024</v>
       </c>
@@ -1829,7 +1829,7 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="37" t="s">
         <v>33</v>
       </c>
